--- a/AAII_Financials/Yearly/BURL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BURL_YR_FIN.xlsx
@@ -1026,7 +1026,7 @@
         <v>51700</v>
       </c>
       <c r="H14" s="3">
-        <v>187500</v>
+        <v>187600</v>
       </c>
       <c r="I14" s="3">
         <v>27100</v>
